--- a/resources/data-imports/Monsters/dungeon-celestials.xlsx
+++ b/resources/data-imports/Monsters/dungeon-celestials.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -341,7 +341,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -365,34 +365,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -538,7 +538,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21"/>
@@ -805,7 +805,7 @@
         <v>0.176192835</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>352385670</v>
+        <v>1000000</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>110.37832</v>
@@ -891,7 +891,7 @@
         <v>0.206959434035581</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>413918868.071163</v>
+        <v>1429969</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>152.29216907528</v>
@@ -977,7 +977,7 @@
         <v>0.243098462751497</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>486196925.502995</v>
+        <v>2044812</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>210.121922146067</v>
@@ -1063,7 +1063,7 @@
         <v>0.285548048908855</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>571096097.817709</v>
+        <v>2924018</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>289.911309520671</v>
@@ -1149,7 +1149,7 @@
         <v>0.335410135106465</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>670820270.21293</v>
+        <v>4181255</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>399.999041173646</v>
@@ -1235,7 +1235,7 @@
         <v>0.393979083947608</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>787958167.895215</v>
+        <v>5979066</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>551.890277079473</v>
@@ -1321,7 +1321,7 @@
         <v>0.462775278209546</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>925550556.419093</v>
+        <v>8549880</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>761.459020104584</v>
@@ -1407,7 +1407,7 @@
         <v>0.543584588237691</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1087169176.47538</v>
+        <v>12226064</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>1050.60709234988</v>
@@ -1493,7 +1493,7 @@
         <v>0.63850473109271</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1277009462.18542</v>
+        <v>17482895</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>1449.5530729208</v>
@@ -1579,7 +1579,7 @@
         <v>0.749999724880915</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1500000000</v>
+        <v>25000000</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>1999.99041174795</v>
